--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/150.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/150.xlsx
@@ -426,13 +426,13 @@
         <v>-3.326634620933389</v>
       </c>
       <c r="E2">
-        <v>-10.33190572111585</v>
+        <v>-12.08170807767967</v>
       </c>
       <c r="F2">
-        <v>-3.539806668570571</v>
+        <v>-3.550408787821481</v>
       </c>
       <c r="G2">
-        <v>-5.585305293611236</v>
+        <v>-6.376095306576944</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.198681082848091</v>
       </c>
       <c r="E3">
-        <v>-11.09138062541625</v>
+        <v>-11.92565233490134</v>
       </c>
       <c r="F3">
-        <v>-3.528955907490938</v>
+        <v>-3.900404627721768</v>
       </c>
       <c r="G3">
-        <v>-4.947558490380494</v>
+        <v>-6.095937079770581</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.069944514652463</v>
       </c>
       <c r="E4">
-        <v>-11.04528076001816</v>
+        <v>-11.74607569812718</v>
       </c>
       <c r="F4">
-        <v>-3.470388879032072</v>
+        <v>-3.452209518828742</v>
       </c>
       <c r="G4">
-        <v>-5.219476769339612</v>
+        <v>-5.628613850355981</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.922099992472215</v>
       </c>
       <c r="E5">
-        <v>-12.04639956584186</v>
+        <v>-13.2814502819538</v>
       </c>
       <c r="F5">
-        <v>-3.627307212251559</v>
+        <v>-3.585784026854652</v>
       </c>
       <c r="G5">
-        <v>-4.953236075980345</v>
+        <v>-6.390410105488752</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.719152482138909</v>
       </c>
       <c r="E6">
-        <v>-12.97724551201454</v>
+        <v>-12.8745533069426</v>
       </c>
       <c r="F6">
-        <v>-3.543589350149599</v>
+        <v>-3.746775651688649</v>
       </c>
       <c r="G6">
-        <v>-4.119604293190928</v>
+        <v>-5.912986401633836</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.430951716269377</v>
       </c>
       <c r="E7">
-        <v>-13.56154998475024</v>
+        <v>-14.05487741467184</v>
       </c>
       <c r="F7">
-        <v>-3.520403103694607</v>
+        <v>-3.493024787681448</v>
       </c>
       <c r="G7">
-        <v>-4.953222833798188</v>
+        <v>-5.36643188582786</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.036468113111575</v>
       </c>
       <c r="E8">
-        <v>-13.74053791990341</v>
+        <v>-14.18698658689761</v>
       </c>
       <c r="F8">
-        <v>-3.399151411396732</v>
+        <v>-3.960775497218319</v>
       </c>
       <c r="G8">
-        <v>-4.24314723162545</v>
+        <v>-5.536309219630022</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.526578376531186</v>
       </c>
       <c r="E9">
-        <v>-14.2694002853632</v>
+        <v>-16.65043569080421</v>
       </c>
       <c r="F9">
-        <v>-3.554977779387523</v>
+        <v>-3.786889338820814</v>
       </c>
       <c r="G9">
-        <v>-3.140656113955202</v>
+        <v>-4.873008315381647</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.9098759432046549</v>
       </c>
       <c r="E10">
-        <v>-15.80707533398572</v>
+        <v>-16.40791779379743</v>
       </c>
       <c r="F10">
-        <v>-3.372706690020725</v>
+        <v>-3.860580758772127</v>
       </c>
       <c r="G10">
-        <v>-3.261484405047522</v>
+        <v>-5.00676428680482</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.2074354862614111</v>
       </c>
       <c r="E11">
-        <v>-15.97712858992176</v>
+        <v>-16.92461214959861</v>
       </c>
       <c r="F11">
-        <v>-3.423478717963798</v>
+        <v>-4.122942231841573</v>
       </c>
       <c r="G11">
-        <v>-2.829766092907784</v>
+        <v>-4.132118155329373</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.5432281663943793</v>
       </c>
       <c r="E12">
-        <v>-16.55784198276938</v>
+        <v>-17.58526216562963</v>
       </c>
       <c r="F12">
-        <v>-3.196878116317933</v>
+        <v>-3.74371593186002</v>
       </c>
       <c r="G12">
-        <v>-2.468410115659716</v>
+        <v>-3.651284589569008</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.299926263575673</v>
       </c>
       <c r="E13">
-        <v>-17.37620516306552</v>
+        <v>-18.59235855714345</v>
       </c>
       <c r="F13">
-        <v>-3.303965934761075</v>
+        <v>-3.295714035088678</v>
       </c>
       <c r="G13">
-        <v>-1.478904606699255</v>
+        <v>-3.296609293219189</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.012945476212102</v>
       </c>
       <c r="E14">
-        <v>-17.44120235049762</v>
+        <v>-18.70853202933623</v>
       </c>
       <c r="F14">
-        <v>-3.176691408866784</v>
+        <v>-3.087645960065286</v>
       </c>
       <c r="G14">
-        <v>-0.6013551267858664</v>
+        <v>-2.613143856091114</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.639826932978795</v>
       </c>
       <c r="E15">
-        <v>-19.05145525204107</v>
+        <v>-19.27550603204457</v>
       </c>
       <c r="F15">
-        <v>-2.835604706593802</v>
+        <v>-3.093709178162546</v>
       </c>
       <c r="G15">
-        <v>-0.5856929358395745</v>
+        <v>-1.383133834793679</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.141667183995747</v>
       </c>
       <c r="E16">
-        <v>-18.51724475877822</v>
+        <v>-19.52695407979447</v>
       </c>
       <c r="F16">
-        <v>-2.64663216564582</v>
+        <v>-3.206806368701823</v>
       </c>
       <c r="G16">
-        <v>-0.3395869804501545</v>
+        <v>-1.736031368188909</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.494089771151791</v>
       </c>
       <c r="E17">
-        <v>-20.78131873754912</v>
+        <v>-20.63218250305452</v>
       </c>
       <c r="F17">
-        <v>-2.511919764919668</v>
+        <v>-2.595680387081345</v>
       </c>
       <c r="G17">
-        <v>0.6086393361811345</v>
+        <v>-0.6921799436557715</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.681616507898852</v>
       </c>
       <c r="E18">
-        <v>-21.95596413887275</v>
+        <v>-22.80360843210249</v>
       </c>
       <c r="F18">
-        <v>-2.201473020992692</v>
+        <v>-2.118246899577476</v>
       </c>
       <c r="G18">
-        <v>1.042009610544969</v>
+        <v>-0.407529306552617</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.70082953380395</v>
       </c>
       <c r="E19">
-        <v>-22.4905912517443</v>
+        <v>-23.96777041609836</v>
       </c>
       <c r="F19">
-        <v>-2.051627518391558</v>
+        <v>-2.309773166314104</v>
       </c>
       <c r="G19">
-        <v>1.523091467220779</v>
+        <v>-0.5071403112837478</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.556001688257915</v>
       </c>
       <c r="E20">
-        <v>-22.79160797598217</v>
+        <v>-23.31127301073238</v>
       </c>
       <c r="F20">
-        <v>-1.591551447720906</v>
+        <v>-1.891776161816678</v>
       </c>
       <c r="G20">
-        <v>1.018799375769138</v>
+        <v>0.256784624630775</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.256887750322327</v>
       </c>
       <c r="E21">
-        <v>-23.01324960781358</v>
+        <v>-24.76307460674745</v>
       </c>
       <c r="F21">
-        <v>-1.442329133397497</v>
+        <v>-1.927369952266179</v>
       </c>
       <c r="G21">
-        <v>1.450193254446027</v>
+        <v>0.5431766086875861</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.819530760759636</v>
       </c>
       <c r="E22">
-        <v>-25.35749116194227</v>
+        <v>-24.67159943179251</v>
       </c>
       <c r="F22">
-        <v>-1.21904560379152</v>
+        <v>-1.388587656862975</v>
       </c>
       <c r="G22">
-        <v>1.485096336066563</v>
+        <v>0.7681149358989062</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.258468495225589</v>
       </c>
       <c r="E23">
-        <v>-25.44168907916689</v>
+        <v>-25.59711536405815</v>
       </c>
       <c r="F23">
-        <v>-0.6644666337347657</v>
+        <v>-1.26845089352957</v>
       </c>
       <c r="G23">
-        <v>1.002955104818186</v>
+        <v>-0.82128128805073</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.595394732733864</v>
       </c>
       <c r="E24">
-        <v>-25.67831090301568</v>
+        <v>-25.75396811826183</v>
       </c>
       <c r="F24">
-        <v>-0.9202074242247162</v>
+        <v>-0.9481922996034891</v>
       </c>
       <c r="G24">
-        <v>1.518973148569926</v>
+        <v>-0.3052698653900693</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.8471601387344111</v>
       </c>
       <c r="E25">
-        <v>-25.46583943104979</v>
+        <v>-27.17298809093537</v>
       </c>
       <c r="F25">
-        <v>-0.7617109280604941</v>
+        <v>-0.9778867855179787</v>
       </c>
       <c r="G25">
-        <v>1.50505561512283</v>
+        <v>-0.4351822934421493</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.04093406807401246</v>
       </c>
       <c r="E26">
-        <v>-25.74884641415915</v>
+        <v>-25.7445624777479</v>
       </c>
       <c r="F26">
-        <v>-0.8350278015628055</v>
+        <v>-1.230054735462698</v>
       </c>
       <c r="G26">
-        <v>0.3299476810486682</v>
+        <v>-0.4238238116969098</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.802451041827528</v>
       </c>
       <c r="E27">
-        <v>-25.78886001049093</v>
+        <v>-26.53589519669226</v>
       </c>
       <c r="F27">
-        <v>-0.6420065164420035</v>
+        <v>-0.6647707052705301</v>
       </c>
       <c r="G27">
-        <v>0.7873127894811398</v>
+        <v>-0.488160953707106</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.652025508152429</v>
       </c>
       <c r="E28">
-        <v>-25.66592099813069</v>
+        <v>-26.70644205629513</v>
       </c>
       <c r="F28">
-        <v>-0.5341181346586066</v>
+        <v>-1.146763682104949</v>
       </c>
       <c r="G28">
-        <v>0.3394224623820624</v>
+        <v>-0.6398931874085224</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.483340354743247</v>
       </c>
       <c r="E29">
-        <v>-25.61996151542685</v>
+        <v>-27.47401840059526</v>
       </c>
       <c r="F29">
-        <v>-0.3484278242203736</v>
+        <v>-1.07309522588941</v>
       </c>
       <c r="G29">
-        <v>0.4127841515323118</v>
+        <v>-0.9488134338600739</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.263861326953124</v>
       </c>
       <c r="E30">
-        <v>-24.81723062740518</v>
+        <v>-26.40512645277277</v>
       </c>
       <c r="F30">
-        <v>-0.8177764930259237</v>
+        <v>-0.8896474430274389</v>
       </c>
       <c r="G30">
-        <v>-0.004678951515324101</v>
+        <v>-1.289018335657738</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.96804287600355</v>
       </c>
       <c r="E31">
-        <v>-24.96250407357124</v>
+        <v>-26.0530421271504</v>
       </c>
       <c r="F31">
-        <v>-0.6725047331085786</v>
+        <v>-1.208573348425677</v>
       </c>
       <c r="G31">
-        <v>-0.30985497096196</v>
+        <v>-0.8648315146198424</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.56844253454551</v>
       </c>
       <c r="E32">
-        <v>-23.96257625641156</v>
+        <v>-25.18575331367538</v>
       </c>
       <c r="F32">
-        <v>-0.6785711186176694</v>
+        <v>-1.070344328714291</v>
       </c>
       <c r="G32">
-        <v>-0.3367101163765278</v>
+        <v>-0.5858584631165381</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.047771217655134</v>
       </c>
       <c r="E33">
-        <v>-23.96811458012294</v>
+        <v>-25.27007802817221</v>
       </c>
       <c r="F33">
-        <v>-0.8568465179598148</v>
+        <v>-1.08790921102243</v>
       </c>
       <c r="G33">
-        <v>-0.6261941499670182</v>
+        <v>-0.653476355756152</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.391879562816098</v>
       </c>
       <c r="E34">
-        <v>-23.92743076963803</v>
+        <v>-26.41289278569592</v>
       </c>
       <c r="F34">
-        <v>-0.8970378066818372</v>
+        <v>-1.655726378826343</v>
       </c>
       <c r="G34">
-        <v>0.168889640563125</v>
+        <v>-1.22119187864915</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.597798665652175</v>
       </c>
       <c r="E35">
-        <v>-23.44744422414303</v>
+        <v>-24.66871026537561</v>
       </c>
       <c r="F35">
-        <v>-1.058637574587363</v>
+        <v>-1.450196984385401</v>
       </c>
       <c r="G35">
-        <v>0.0274929300353133</v>
+        <v>-0.5750064948388072</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.667437390877812</v>
       </c>
       <c r="E36">
-        <v>-22.47730018053179</v>
+        <v>-23.9343231070777</v>
       </c>
       <c r="F36">
-        <v>-0.7329817109014648</v>
+        <v>-1.268633811562803</v>
       </c>
       <c r="G36">
-        <v>-0.1282516848596997</v>
+        <v>-0.2319147973308984</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.613527496571757</v>
       </c>
       <c r="E37">
-        <v>-22.10313501564803</v>
+        <v>-24.28390771504783</v>
       </c>
       <c r="F37">
-        <v>-1.150588331890735</v>
+        <v>-1.190434372723191</v>
       </c>
       <c r="G37">
-        <v>0.3753782974840867</v>
+        <v>-0.8575483144334458</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.451689009431766</v>
       </c>
       <c r="E38">
-        <v>-22.01694004138603</v>
+        <v>-23.71247316544193</v>
       </c>
       <c r="F38">
-        <v>-1.105119343205511</v>
+        <v>-1.451197886523958</v>
       </c>
       <c r="G38">
-        <v>0.1439943381078056</v>
+        <v>-1.38113095474242</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.206886040646731</v>
       </c>
       <c r="E39">
-        <v>-22.82177666982126</v>
+        <v>-23.14034575931286</v>
       </c>
       <c r="F39">
-        <v>-1.162969744737641</v>
+        <v>-1.744511308004752</v>
       </c>
       <c r="G39">
-        <v>0.09335623353911356</v>
+        <v>-0.1613041715237832</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.902650643905638</v>
       </c>
       <c r="E40">
-        <v>-21.47667044990092</v>
+        <v>-22.53983387810371</v>
       </c>
       <c r="F40">
-        <v>-0.8543078373773654</v>
+        <v>-1.241990335094407</v>
       </c>
       <c r="G40">
-        <v>0.421782214308051</v>
+        <v>-0.6201093672658378</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.570038194311201</v>
       </c>
       <c r="E41">
-        <v>-20.83431546886089</v>
+        <v>-21.4771912244118</v>
       </c>
       <c r="F41">
-        <v>-0.9819577015736157</v>
+        <v>-1.325090551889346</v>
       </c>
       <c r="G41">
-        <v>0.102920399602068</v>
+        <v>-0.9077692902641897</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.232082743407958</v>
       </c>
       <c r="E42">
-        <v>-20.21578931804923</v>
+        <v>-20.65922202135432</v>
       </c>
       <c r="F42">
-        <v>-0.7894424104927965</v>
+        <v>-1.405081953972277</v>
       </c>
       <c r="G42">
-        <v>0.8586815302167481</v>
+        <v>-0.7272485525532713</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.917451376274517</v>
       </c>
       <c r="E43">
-        <v>-20.0337582483629</v>
+        <v>-21.19397140302408</v>
       </c>
       <c r="F43">
-        <v>-1.087458646689488</v>
+        <v>-1.653801384286127</v>
       </c>
       <c r="G43">
-        <v>0.8080334940114382</v>
+        <v>-1.238618590367874</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.642333689466741</v>
       </c>
       <c r="E44">
-        <v>-20.31945061655881</v>
+        <v>-19.9654507464312</v>
       </c>
       <c r="F44">
-        <v>-1.249891443906535</v>
+        <v>-1.243971551194622</v>
       </c>
       <c r="G44">
-        <v>1.625499882932594</v>
+        <v>-0.3075408996300094</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.427430112649057</v>
       </c>
       <c r="E45">
-        <v>-19.34485055452403</v>
+        <v>-19.48657367706808</v>
       </c>
       <c r="F45">
-        <v>-1.000076880952159</v>
+        <v>-1.381597178952225</v>
       </c>
       <c r="G45">
-        <v>0.7823933188097828</v>
+        <v>-0.9048626312807097</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.278122726888265</v>
       </c>
       <c r="E46">
-        <v>-18.34533030002503</v>
+        <v>-20.05982867322506</v>
       </c>
       <c r="F46">
-        <v>-1.292688720712412</v>
+        <v>-1.075013885605965</v>
       </c>
       <c r="G46">
-        <v>0.5020199065433667</v>
+        <v>-1.21169723404252</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.203792949852568</v>
       </c>
       <c r="E47">
-        <v>-17.64702602262024</v>
+        <v>-19.11742606138481</v>
       </c>
       <c r="F47">
-        <v>-1.351424413851273</v>
+        <v>-1.522001418738467</v>
       </c>
       <c r="G47">
-        <v>0.1863329050095449</v>
+        <v>-1.402672674566457</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.199115490146366</v>
       </c>
       <c r="E48">
-        <v>-18.00856127349661</v>
+        <v>-19.07960424647275</v>
       </c>
       <c r="F48">
-        <v>-1.405825503899576</v>
+        <v>-1.328323687515716</v>
       </c>
       <c r="G48">
-        <v>1.158828830989231</v>
+        <v>0.1532208285257544</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.262419418577315</v>
       </c>
       <c r="E49">
-        <v>-17.57382776876026</v>
+        <v>-17.52127029942724</v>
       </c>
       <c r="F49">
-        <v>-1.116838766979763</v>
+        <v>-1.466569336139214</v>
       </c>
       <c r="G49">
-        <v>0.3356153350119005</v>
+        <v>-1.309643034367398</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.381552018420797</v>
       </c>
       <c r="E50">
-        <v>-17.15655153132347</v>
+        <v>-16.96280982785331</v>
       </c>
       <c r="F50">
-        <v>-1.334076499253549</v>
+        <v>-1.378834403982741</v>
       </c>
       <c r="G50">
-        <v>0.2783892448200587</v>
+        <v>-1.923447972258129</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.546163677302878</v>
       </c>
       <c r="E51">
-        <v>-16.3300869110276</v>
+        <v>-17.26734970486914</v>
       </c>
       <c r="F51">
-        <v>-1.202222687704765</v>
+        <v>-1.61539651583672</v>
       </c>
       <c r="G51">
-        <v>0.1254453514512692</v>
+        <v>-1.348181094990054</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.740090635664</v>
       </c>
       <c r="E52">
-        <v>-15.7217543552072</v>
+        <v>-16.60761444058768</v>
       </c>
       <c r="F52">
-        <v>-1.26301957409257</v>
+        <v>-1.442720308758611</v>
       </c>
       <c r="G52">
-        <v>0.05202076193577352</v>
+        <v>-1.25544278279845</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.948344501446131</v>
       </c>
       <c r="E53">
-        <v>-15.50239054580164</v>
+        <v>-16.24704828314895</v>
       </c>
       <c r="F53">
-        <v>-1.575350136205961</v>
+        <v>-1.525362834543988</v>
       </c>
       <c r="G53">
-        <v>-0.06825466805148797</v>
+        <v>-1.759724942613473</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.156277318837745</v>
       </c>
       <c r="E54">
-        <v>-14.59318617691163</v>
+        <v>-16.17725544174273</v>
       </c>
       <c r="F54">
-        <v>-1.635492952050689</v>
+        <v>-1.306888227950243</v>
       </c>
       <c r="G54">
-        <v>-1.032209386539855</v>
+        <v>-2.092805550410625</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.349817657636252</v>
       </c>
       <c r="E55">
-        <v>-14.62301976367416</v>
+        <v>-16.0354281642965</v>
       </c>
       <c r="F55">
-        <v>-1.421565956993128</v>
+        <v>-1.846407738457084</v>
       </c>
       <c r="G55">
-        <v>-0.3514652178450595</v>
+        <v>-1.160012997083419</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.519749125688025</v>
       </c>
       <c r="E56">
-        <v>-14.21348268831648</v>
+        <v>-14.78637993502686</v>
       </c>
       <c r="F56">
-        <v>-1.604359669312023</v>
+        <v>-1.84240492175581</v>
       </c>
       <c r="G56">
-        <v>-0.1018467736384727</v>
+        <v>-1.649069957963333</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.656831443417892</v>
       </c>
       <c r="E57">
-        <v>-14.3450303297653</v>
+        <v>-15.16976054451623</v>
       </c>
       <c r="F57">
-        <v>-1.371818586777344</v>
+        <v>-1.38311991218992</v>
       </c>
       <c r="G57">
-        <v>-1.12217015102401</v>
+        <v>-1.324173018739259</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.758971136812851</v>
       </c>
       <c r="E58">
-        <v>-13.73010884426374</v>
+        <v>-13.84803030742348</v>
       </c>
       <c r="F58">
-        <v>-1.647392918299301</v>
+        <v>-1.413118469640174</v>
       </c>
       <c r="G58">
-        <v>-1.300681387592591</v>
+        <v>-3.012763118682078</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.821903874624304</v>
       </c>
       <c r="E59">
-        <v>-13.39969326676808</v>
+        <v>-13.84596079480197</v>
       </c>
       <c r="F59">
-        <v>-1.708811409258916</v>
+        <v>-1.159532311048179</v>
       </c>
       <c r="G59">
-        <v>-1.109189501964527</v>
+        <v>-2.447768864222361</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.848721561363726</v>
       </c>
       <c r="E60">
-        <v>-13.6348523935124</v>
+        <v>-13.70128057873091</v>
       </c>
       <c r="F60">
-        <v>-1.763612385050867</v>
+        <v>-1.902103508091258</v>
       </c>
       <c r="G60">
-        <v>-1.727519955607443</v>
+        <v>-3.177770639995972</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.837773241244391</v>
       </c>
       <c r="E61">
-        <v>-13.11090795082494</v>
+        <v>-13.63670453938153</v>
       </c>
       <c r="F61">
-        <v>-1.848156149787729</v>
+        <v>-1.541161092903454</v>
       </c>
       <c r="G61">
-        <v>-1.579806724190701</v>
+        <v>-3.262785449444455</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.794642477065881</v>
       </c>
       <c r="E62">
-        <v>-12.93741758311708</v>
+        <v>-13.88316220877499</v>
       </c>
       <c r="F62">
-        <v>-1.774393463070221</v>
+        <v>-1.591298846627393</v>
       </c>
       <c r="G62">
-        <v>-1.705796155778745</v>
+        <v>-3.348879496738742</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.718838159508778</v>
       </c>
       <c r="E63">
-        <v>-12.71604313125211</v>
+        <v>-12.42101304965239</v>
       </c>
       <c r="F63">
-        <v>-2.139219125162683</v>
+        <v>-1.822648190460703</v>
       </c>
       <c r="G63">
-        <v>-1.789317909189018</v>
+        <v>-2.425945748027485</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.615493717304145</v>
       </c>
       <c r="E64">
-        <v>-12.95871046790114</v>
+        <v>-13.09164835087031</v>
       </c>
       <c r="F64">
-        <v>-2.236894187497411</v>
+        <v>-1.883426864230481</v>
       </c>
       <c r="G64">
-        <v>-1.815179890941804</v>
+        <v>-3.79871973516045</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.482665334544482</v>
       </c>
       <c r="E65">
-        <v>-12.54014814384618</v>
+        <v>-12.67362038674826</v>
       </c>
       <c r="F65">
-        <v>-1.965483418827145</v>
+        <v>-2.071035834385269</v>
       </c>
       <c r="G65">
-        <v>-1.907838750040466</v>
+        <v>-3.842680469376432</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.323552420193261</v>
       </c>
       <c r="E66">
-        <v>-12.64600575224948</v>
+        <v>-12.44904883223387</v>
       </c>
       <c r="F66">
-        <v>-2.332380568257002</v>
+        <v>-1.904046715249502</v>
       </c>
       <c r="G66">
-        <v>-1.97931673877887</v>
+        <v>-3.777267400065973</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.135810249111421</v>
       </c>
       <c r="E67">
-        <v>-12.83481594752529</v>
+        <v>-12.54718086398009</v>
       </c>
       <c r="F67">
-        <v>-1.788746589781849</v>
+        <v>-2.116454936334156</v>
       </c>
       <c r="G67">
-        <v>-2.275382136901431</v>
+        <v>-4.158774668011585</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.923488196919723</v>
       </c>
       <c r="E68">
-        <v>-12.28353763572753</v>
+        <v>-11.62637454468242</v>
       </c>
       <c r="F68">
-        <v>-2.000171329493015</v>
+        <v>-2.185084040326768</v>
       </c>
       <c r="G68">
-        <v>-2.448622984971493</v>
+        <v>-4.454767234132282</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.68520168057765</v>
       </c>
       <c r="E69">
-        <v>-12.18110355367403</v>
+        <v>-11.85765276920216</v>
       </c>
       <c r="F69">
-        <v>-2.149439571287972</v>
+        <v>-2.640042365331677</v>
       </c>
       <c r="G69">
-        <v>-2.171305206237824</v>
+        <v>-4.816798562670361</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.426435363362304</v>
       </c>
       <c r="E70">
-        <v>-13.14251217092447</v>
+        <v>-12.56564798098337</v>
       </c>
       <c r="F70">
-        <v>-2.152126328373515</v>
+        <v>-2.645466558092057</v>
       </c>
       <c r="G70">
-        <v>-2.566730007630531</v>
+        <v>-3.718720402203962</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.147584910868313</v>
       </c>
       <c r="E71">
-        <v>-11.42002556957491</v>
+        <v>-12.33837292748641</v>
       </c>
       <c r="F71">
-        <v>-2.649881138331344</v>
+        <v>-2.684095520928498</v>
       </c>
       <c r="G71">
-        <v>-2.590363992235388</v>
+        <v>-4.12708612610968</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.856913743960602</v>
       </c>
       <c r="E72">
-        <v>-13.09055698863447</v>
+        <v>-12.56001455931783</v>
       </c>
       <c r="F72">
-        <v>-2.38712373878304</v>
+        <v>-2.341696718304574</v>
       </c>
       <c r="G72">
-        <v>-2.839469301883388</v>
+        <v>-3.884850198455668</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.557259528677069</v>
       </c>
       <c r="E73">
-        <v>-12.20443425176155</v>
+        <v>-11.27624199135737</v>
       </c>
       <c r="F73">
-        <v>-2.931764162367454</v>
+        <v>-2.51822529002199</v>
       </c>
       <c r="G73">
-        <v>-2.563505536275281</v>
+        <v>-3.988288193830197</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.259673800976822</v>
       </c>
       <c r="E74">
-        <v>-13.30647010084618</v>
+        <v>-11.93269411198327</v>
       </c>
       <c r="F74">
-        <v>-2.736163812163359</v>
+        <v>-2.490613377386303</v>
       </c>
       <c r="G74">
-        <v>-2.881351013500708</v>
+        <v>-4.472971924052734</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.968794000404044</v>
       </c>
       <c r="E75">
-        <v>-12.6985632215825</v>
+        <v>-12.79342569509518</v>
       </c>
       <c r="F75">
-        <v>-2.532693235412487</v>
+        <v>-2.68700162128333</v>
       </c>
       <c r="G75">
-        <v>-1.81637830842702</v>
+        <v>-3.350541390599456</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.696436145572144</v>
       </c>
       <c r="E76">
-        <v>-13.27006569829852</v>
+        <v>-13.63381537296464</v>
       </c>
       <c r="F76">
-        <v>-2.985289463044519</v>
+        <v>-2.709637529932706</v>
       </c>
       <c r="G76">
-        <v>-2.34978995844209</v>
+        <v>-3.854267378763881</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.447171014352316</v>
       </c>
       <c r="E77">
-        <v>-13.42482176903665</v>
+        <v>-14.45721421635732</v>
       </c>
       <c r="F77">
-        <v>-2.94474263234448</v>
+        <v>-2.66105418356477</v>
       </c>
       <c r="G77">
-        <v>-2.314810734274151</v>
+        <v>-3.486426042804381</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.232024605555313</v>
       </c>
       <c r="E78">
-        <v>-14.14882966490897</v>
+        <v>-13.76253271815866</v>
       </c>
       <c r="F78">
-        <v>-2.696084174708375</v>
+        <v>-2.726112822571022</v>
       </c>
       <c r="G78">
-        <v>-2.160337368866218</v>
+        <v>-3.681920377989424</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.054140367339204</v>
       </c>
       <c r="E79">
-        <v>-14.29011352547428</v>
+        <v>-13.93930170104808</v>
       </c>
       <c r="F79">
-        <v>-3.038227208826955</v>
+        <v>-2.566559202708244</v>
       </c>
       <c r="G79">
-        <v>-2.567792692748637</v>
+        <v>-2.979151149821857</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.9219626227677785</v>
       </c>
       <c r="E80">
-        <v>-15.50348190803749</v>
+        <v>-14.66828186138082</v>
       </c>
       <c r="F80">
-        <v>-2.710789675986188</v>
+        <v>-2.780000000049765</v>
       </c>
       <c r="G80">
-        <v>-2.48606194447511</v>
+        <v>-3.683694830398473</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.8360046156785377</v>
       </c>
       <c r="E81">
-        <v>-16.05428020159044</v>
+        <v>-15.03028807355399</v>
       </c>
       <c r="F81">
-        <v>-2.906263329717048</v>
+        <v>-3.036173934107588</v>
       </c>
       <c r="G81">
-        <v>-1.679268754372565</v>
+        <v>-2.841899242309213</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.7999081720077249</v>
       </c>
       <c r="E82">
-        <v>-16.97010972795368</v>
+        <v>-16.46285724045849</v>
       </c>
       <c r="F82">
-        <v>-2.957090787367162</v>
+        <v>-3.053400695202781</v>
       </c>
       <c r="G82">
-        <v>-1.615928086569689</v>
+        <v>-2.946774014447785</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.810403842661571</v>
       </c>
       <c r="E83">
-        <v>-17.52545460941032</v>
+        <v>-17.16301366373242</v>
       </c>
       <c r="F83">
-        <v>-2.805678999615658</v>
+        <v>-2.754321000483872</v>
       </c>
       <c r="G83">
-        <v>-2.398716510966979</v>
+        <v>-3.007744331644543</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.8653917596561191</v>
       </c>
       <c r="E84">
-        <v>-18.29322567809278</v>
+        <v>-17.15666474317366</v>
       </c>
       <c r="F84">
-        <v>-2.667312197489629</v>
+        <v>-3.284916328157212</v>
       </c>
       <c r="G84">
-        <v>-1.388675688026419</v>
+        <v>-2.543807790316618</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.9586684770864679</v>
       </c>
       <c r="E85">
-        <v>-18.84533270063394</v>
+        <v>-19.02258623024217</v>
       </c>
       <c r="F85">
-        <v>-3.230501776608628</v>
+        <v>-2.662171488088112</v>
       </c>
       <c r="G85">
-        <v>-1.441475578832255</v>
+        <v>-1.935203719468081</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.083900736735236</v>
       </c>
       <c r="E86">
-        <v>-21.15865836271227</v>
+        <v>-19.50318411972821</v>
       </c>
       <c r="F86">
-        <v>-2.715677784294192</v>
+        <v>-3.192091365188517</v>
       </c>
       <c r="G86">
-        <v>-0.9711596162501545</v>
+        <v>-2.225290272346719</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.233200283936954</v>
       </c>
       <c r="E87">
-        <v>-21.13418196070081</v>
+        <v>-21.69814452819405</v>
       </c>
       <c r="F87">
-        <v>-2.883070748438395</v>
+        <v>-3.150393180287954</v>
       </c>
       <c r="G87">
-        <v>-1.265927280521322</v>
+        <v>-2.262226028928368</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.397724881163336</v>
       </c>
       <c r="E88">
-        <v>-23.57274257146126</v>
+        <v>-21.56009399807022</v>
       </c>
       <c r="F88">
-        <v>-3.155666920986368</v>
+        <v>-2.738511656182998</v>
       </c>
       <c r="G88">
-        <v>-0.9861232820876602</v>
+        <v>-2.134601187843924</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.569143640526266</v>
       </c>
       <c r="E89">
-        <v>-25.38866970548509</v>
+        <v>-24.55968272516694</v>
       </c>
       <c r="F89">
-        <v>-3.078435918314047</v>
+        <v>-2.976584623480306</v>
       </c>
       <c r="G89">
-        <v>-0.6490302930969108</v>
+        <v>-2.753418291681112</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.736944227460496</v>
       </c>
       <c r="E90">
-        <v>-25.89320058010166</v>
+        <v>-24.87843295361884</v>
       </c>
       <c r="F90">
-        <v>-2.793031524174958</v>
+        <v>-2.935954648219707</v>
       </c>
       <c r="G90">
-        <v>-0.5339623512429229</v>
+        <v>-1.866407272616487</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.893808961369741</v>
       </c>
       <c r="E91">
-        <v>-29.7888860080732</v>
+        <v>-29.13339618817393</v>
       </c>
       <c r="F91">
-        <v>-2.823812432347439</v>
+        <v>-2.679683316248084</v>
       </c>
       <c r="G91">
-        <v>-1.112781443874637</v>
+        <v>-2.15883107064585</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.032308511024003</v>
       </c>
       <c r="E92">
-        <v>-29.97972043123044</v>
+        <v>-30.35273309947925</v>
       </c>
       <c r="F92">
-        <v>-2.856490620206617</v>
+        <v>-2.856439941617323</v>
       </c>
       <c r="G92">
-        <v>-0.9574142311711005</v>
+        <v>-2.289206975073428</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.152180638763642</v>
       </c>
       <c r="E93">
-        <v>-33.26215085213524</v>
+        <v>-31.77334256652948</v>
       </c>
       <c r="F93">
-        <v>-2.833419192430495</v>
+        <v>-3.091623437471912</v>
       </c>
       <c r="G93">
-        <v>-0.9699049194907706</v>
+        <v>-2.386368176105498</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.252511777904821</v>
       </c>
       <c r="E94">
-        <v>-35.00204717180728</v>
+        <v>-34.54269461812823</v>
       </c>
       <c r="F94">
-        <v>-3.033537063758382</v>
+        <v>-2.833175301719518</v>
       </c>
       <c r="G94">
-        <v>-1.916479273897963</v>
+        <v>-2.046600266319017</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.338145916016389</v>
       </c>
       <c r="E95">
-        <v>-36.91181107998106</v>
+        <v>-36.43912443458641</v>
       </c>
       <c r="F95">
-        <v>-3.052261218796622</v>
+        <v>-2.9608695096814</v>
       </c>
       <c r="G95">
-        <v>-1.866883991174142</v>
+        <v>-2.576118714779904</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.408421919855493</v>
       </c>
       <c r="E96">
-        <v>-39.46097513990485</v>
+        <v>-37.61790433267904</v>
       </c>
       <c r="F96">
-        <v>-2.767320850490757</v>
+        <v>-2.943916729709579</v>
       </c>
       <c r="G96">
-        <v>-1.750928823115629</v>
+        <v>-2.346995858006946</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.467568018660639</v>
       </c>
       <c r="E97">
-        <v>-40.96950040133999</v>
+        <v>-40.45230564916096</v>
       </c>
       <c r="F97">
-        <v>-3.008459080587398</v>
+        <v>-3.519860684418569</v>
       </c>
       <c r="G97">
-        <v>-2.025651134146509</v>
+        <v>-4.020165436827839</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.511328312826698</v>
       </c>
       <c r="E98">
-        <v>-43.51562359096764</v>
+        <v>-41.85758623169524</v>
       </c>
       <c r="F98">
-        <v>-2.889492675925502</v>
+        <v>-3.023642861051674</v>
       </c>
       <c r="G98">
-        <v>-2.02501219885743</v>
+        <v>-2.970586768511763</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.542704915856584</v>
       </c>
       <c r="E99">
-        <v>-46.34803690736019</v>
+        <v>-46.08516578392594</v>
       </c>
       <c r="F99">
-        <v>-3.138919230930596</v>
+        <v>-3.296879642642441</v>
       </c>
       <c r="G99">
-        <v>-2.853532499334212</v>
+        <v>-3.493083549883856</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.551418972032007</v>
       </c>
       <c r="E100">
-        <v>-48.78968593739387</v>
+        <v>-47.5500682552452</v>
       </c>
       <c r="F100">
-        <v>-3.166873224044017</v>
+        <v>-2.972785312989167</v>
       </c>
       <c r="G100">
-        <v>-2.850159053429695</v>
+        <v>-4.391711273245784</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.541232321347196</v>
       </c>
       <c r="E101">
-        <v>-50.4242431589365</v>
+        <v>-49.85692159584806</v>
       </c>
       <c r="F101">
-        <v>-2.845433185505019</v>
+        <v>-3.484650150800604</v>
       </c>
       <c r="G101">
-        <v>-3.383739541267268</v>
+        <v>-3.739311995458229</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.490904885903441</v>
       </c>
       <c r="E102">
-        <v>-52.28456632001302</v>
+        <v>-51.46229846300376</v>
       </c>
       <c r="F102">
-        <v>-3.258189707128256</v>
+        <v>-3.070537185060793</v>
       </c>
       <c r="G102">
-        <v>-3.519117680004684</v>
+        <v>-3.744406925043167</v>
       </c>
     </row>
   </sheetData>
